--- a/Box.xlsx
+++ b/Box.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93836082-51FF-4ED8-BF75-4759BC000DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD3D481-E4AC-4735-8459-A34481FB32FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E691B2DF-0B84-4897-BBED-FB46147BB5E9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{E691B2DF-0B84-4897-BBED-FB46147BB5E9}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$F$1</definedName>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="50">
   <si>
     <t>Carta</t>
   </si>
@@ -150,6 +151,48 @@
   </si>
   <si>
     <t>Vampiric Tutor</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>Pessoas</t>
+  </si>
+  <si>
+    <t>Vivian</t>
+  </si>
+  <si>
+    <t>Hamster</t>
+  </si>
+  <si>
+    <t>Dexter</t>
+  </si>
+  <si>
+    <t>Talita</t>
+  </si>
+  <si>
+    <t>João</t>
+  </si>
+  <si>
+    <t>Castor</t>
+  </si>
+  <si>
+    <t>Philips</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Por Pessoa</t>
+  </si>
+  <si>
+    <t>Pago</t>
+  </si>
+  <si>
+    <t>Faltam</t>
+  </si>
+  <si>
+    <t>Vendas</t>
   </si>
 </sst>
 </file>
@@ -188,7 +231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -197,6 +240,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -936,7 +982,7 @@
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>26</v>
       </c>
@@ -947,7 +993,7 @@
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>26</v>
       </c>
@@ -958,7 +1004,7 @@
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>22</v>
       </c>
@@ -969,18 +1015,25 @@
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>35</v>
       </c>
       <c r="B36" s="3">
         <v>649</v>
       </c>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
+      <c r="C36" s="3">
+        <v>630</v>
+      </c>
+      <c r="D36" s="3">
+        <v>600</v>
+      </c>
       <c r="E36" s="3"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F36" s="2">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>23</v>
       </c>
@@ -1000,4 +1053,172 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9EECFB0-024E-43AC-9C9D-6CD7AD46EEA3}">
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="14.5703125" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="1">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1962.41</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="4">
+        <v>245.3</v>
+      </c>
+      <c r="E2" s="4">
+        <v>245.3</v>
+      </c>
+      <c r="F2" s="4">
+        <v>259.47000000000003</v>
+      </c>
+      <c r="G2" s="4">
+        <v>245.63</v>
+      </c>
+      <c r="H2" s="4">
+        <v>245.63</v>
+      </c>
+      <c r="I2" s="4">
+        <v>104</v>
+      </c>
+      <c r="J2" s="4">
+        <v>259.47000000000003</v>
+      </c>
+      <c r="K2" s="4">
+        <v>259.47000000000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" s="4">
+        <f>B2/B1</f>
+        <v>245.30125000000001</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="4">
+        <f>D2-$B$3</f>
+        <v>-1.2499999999988631E-3</v>
+      </c>
+      <c r="E3" s="4">
+        <f>E2-$B$3</f>
+        <v>-1.2499999999988631E-3</v>
+      </c>
+      <c r="F3" s="4">
+        <f>F2-$B$3</f>
+        <v>14.168750000000017</v>
+      </c>
+      <c r="G3" s="4">
+        <f>G2-$B$3</f>
+        <v>0.32874999999998522</v>
+      </c>
+      <c r="H3" s="4">
+        <f>H2-$B$3</f>
+        <v>0.32874999999998522</v>
+      </c>
+      <c r="I3" s="4">
+        <f>I2-$B$3</f>
+        <v>-141.30125000000001</v>
+      </c>
+      <c r="J3" s="4">
+        <f>J2-$B$3</f>
+        <v>14.168750000000017</v>
+      </c>
+      <c r="K3" s="4">
+        <f>K2-$B$3</f>
+        <v>14.168750000000017</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="1">
+        <v>600</v>
+      </c>
+      <c r="C6" s="1">
+        <f>B6/8</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="1">
+        <v>42.4</v>
+      </c>
+      <c r="C7" s="1">
+        <f>B7/8</f>
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="1">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1">
+        <f>B8/8</f>
+        <v>2.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>